--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008444969144207771</v>
       </c>
       <c r="C2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>35721932</v>
+        <v>4042294</v>
       </c>
       <c r="L2" t="n">
-        <v>20051397</v>
+        <v>1975585</v>
       </c>
       <c r="M2" t="n">
-        <v>4727462</v>
+        <v>398496</v>
       </c>
       <c r="N2" t="n">
-        <v>226663</v>
+        <v>13683</v>
       </c>
       <c r="O2" t="n">
-        <v>2836252</v>
+        <v>239219</v>
       </c>
       <c r="P2" t="n">
-        <v>1087831</v>
+        <v>95380</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999847412109375</v>
+        <v>0.9999845027923584</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8734414577484131</v>
+        <v>0.7806908488273621</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7540025115013123</v>
+        <v>0.5954273343086243</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7058131098747253</v>
+        <v>0.4989407658576965</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2762417793273926</v>
+        <v>0.09232045710086823</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7414522171020508</v>
+        <v>0.5502702593803406</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8385133147239685</v>
+        <v>0.6855557560920715</v>
       </c>
       <c r="X2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="AG2" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AH2" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AI2" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9562234282493591</v>
+        <v>0.9553927183151245</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114547371864319</v>
+        <v>0.9118788242340088</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582150936126709</v>
+        <v>0.85825514793396</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619678735733032</v>
+        <v>0.661193311214447</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020171165466309</v>
+        <v>0.9019849300384521</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002024809124862332</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>35721932</v>
+        <v>4042294</v>
       </c>
       <c r="E3" t="n">
-        <v>4312478</v>
+        <v>910242</v>
       </c>
       <c r="F3" t="n">
-        <v>90688</v>
+        <v>31135</v>
       </c>
       <c r="G3" t="n">
-        <v>9146</v>
+        <v>2850</v>
       </c>
       <c r="H3" t="n">
-        <v>5407</v>
+        <v>2026</v>
       </c>
       <c r="I3" t="n">
-        <v>306</v>
+        <v>132</v>
       </c>
       <c r="J3" t="n">
-        <v>80132205</v>
+        <v>10016524</v>
       </c>
       <c r="K3" t="n">
-        <v>85320848</v>
+        <v>10205368</v>
       </c>
       <c r="L3" t="n">
-        <v>97911057</v>
+        <v>11691346</v>
       </c>
       <c r="M3" t="n">
-        <v>121195549</v>
+        <v>14991472</v>
       </c>
       <c r="N3" t="n">
-        <v>129328880</v>
+        <v>16105467</v>
       </c>
       <c r="O3" t="n">
-        <v>125570646</v>
+        <v>15623196</v>
       </c>
       <c r="P3" t="n">
-        <v>128880176</v>
+        <v>16092262</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8899341225624084</v>
+        <v>0.810292661190033</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7657921314239502</v>
+        <v>0.5994048118591309</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6327903866767883</v>
+        <v>0.4248630106449127</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3174289464950562</v>
+        <v>0.1527052372694016</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6956474184989929</v>
+        <v>0.4682369828224182</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7031320333480835</v>
+        <v>0.4926907420158386</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="Z3" t="n">
-        <v>1581425</v>
+        <v>197221</v>
       </c>
       <c r="AA3" t="n">
-        <v>68001</v>
+        <v>8441</v>
       </c>
       <c r="AB3" t="n">
-        <v>54459</v>
+        <v>6838</v>
       </c>
       <c r="AC3" t="n">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80132976</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>88737218</v>
+        <v>11117918</v>
       </c>
       <c r="AG3" t="n">
-        <v>102138438</v>
+        <v>12743989</v>
       </c>
       <c r="AH3" t="n">
-        <v>122107746</v>
+        <v>15258909</v>
       </c>
       <c r="AI3" t="n">
-        <v>129681597</v>
+        <v>16209685</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126160401</v>
+        <v>15768676</v>
       </c>
       <c r="AK3" t="n">
-        <v>128983636</v>
+        <v>16122748</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575390219688416</v>
+        <v>0.9573953747749329</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098982810974121</v>
+        <v>0.909557044506073</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573940396308899</v>
+        <v>0.8569823503494263</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613346934318542</v>
+        <v>0.6601602435112</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014958739280701</v>
+        <v>0.9011887311935425</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0319507024117701</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4856399</v>
+        <v>1053091</v>
       </c>
       <c r="E4" t="n">
-        <v>20051397</v>
+        <v>1975585</v>
       </c>
       <c r="F4" t="n">
-        <v>1098144</v>
+        <v>214986</v>
       </c>
       <c r="G4" t="n">
-        <v>68046</v>
+        <v>20337</v>
       </c>
       <c r="H4" t="n">
-        <v>100901</v>
+        <v>28806</v>
       </c>
       <c r="I4" t="n">
-        <v>8942</v>
+        <v>3101</v>
       </c>
       <c r="J4" t="n">
-        <v>771</v>
+        <v>98</v>
       </c>
       <c r="K4" t="n">
-        <v>5175979</v>
+        <v>1135548</v>
       </c>
       <c r="L4" t="n">
-        <v>6541879</v>
+        <v>1342343</v>
       </c>
       <c r="M4" t="n">
-        <v>1970433</v>
+        <v>400188</v>
       </c>
       <c r="N4" t="n">
-        <v>593861</v>
+        <v>134529</v>
       </c>
       <c r="O4" t="n">
-        <v>989014</v>
+        <v>195511</v>
       </c>
       <c r="P4" t="n">
-        <v>209502</v>
+        <v>43748</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999923706054688</v>
+        <v>0.9999922513961792</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8816106915473938</v>
+        <v>0.7952163815498352</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7598515748977661</v>
+        <v>0.5974094867706299</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6673099994659424</v>
+        <v>0.4589318037033081</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2954066395759583</v>
+        <v>0.1150721535086632</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7178198099136353</v>
+        <v>0.5059500336647034</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7648783326148987</v>
+        <v>0.5733383893966675</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1643061</v>
+        <v>208344</v>
       </c>
       <c r="Z4" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AA4" t="n">
-        <v>662423</v>
+        <v>82986</v>
       </c>
       <c r="AB4" t="n">
-        <v>44064</v>
+        <v>5563</v>
       </c>
       <c r="AC4" t="n">
-        <v>9119</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1759609</v>
+        <v>222998</v>
       </c>
       <c r="AG4" t="n">
-        <v>2314498</v>
+        <v>289700</v>
       </c>
       <c r="AH4" t="n">
-        <v>1058236</v>
+        <v>132751</v>
       </c>
       <c r="AI4" t="n">
-        <v>241144</v>
+        <v>30311</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399259</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568807482719421</v>
+        <v>0.9563930034637451</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106758832931519</v>
+        <v>0.9107164144515991</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578044176101685</v>
+        <v>0.8576182723045349</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616511344909668</v>
+        <v>0.6606763601303101</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017564058303833</v>
+        <v>0.901586651802063</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>218043</v>
+        <v>60324</v>
       </c>
       <c r="E5" t="n">
-        <v>1861757</v>
+        <v>345284</v>
       </c>
       <c r="F5" t="n">
-        <v>4727462</v>
+        <v>398496</v>
       </c>
       <c r="G5" t="n">
-        <v>196051</v>
+        <v>42689</v>
       </c>
       <c r="H5" t="n">
-        <v>428384</v>
+        <v>80614</v>
       </c>
       <c r="I5" t="n">
-        <v>39071</v>
+        <v>10527</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4418041</v>
+        <v>946390</v>
       </c>
       <c r="L5" t="n">
-        <v>6132467</v>
+        <v>1320326</v>
       </c>
       <c r="M5" t="n">
-        <v>2743356</v>
+        <v>539444</v>
       </c>
       <c r="N5" t="n">
-        <v>487396</v>
+        <v>75921</v>
       </c>
       <c r="O5" t="n">
-        <v>1240888</v>
+        <v>271674</v>
       </c>
       <c r="P5" t="n">
-        <v>459291</v>
+        <v>98210</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999940991401672</v>
+        <v>0.9999939799308777</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9265595674514771</v>
+        <v>0.872505247592926</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9029802680015564</v>
+        <v>0.836942195892334</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9639168381690979</v>
+        <v>0.9424583315849304</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9917231798171997</v>
+        <v>0.9871123433113098</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9829305410385132</v>
+        <v>0.9713903069496155</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9948804974555969</v>
+        <v>0.9913067221641541</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64236</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>683114</v>
+        <v>86223</v>
       </c>
       <c r="AA5" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AB5" t="n">
-        <v>79701</v>
+        <v>9997</v>
       </c>
       <c r="AC5" t="n">
-        <v>233268</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1704383</v>
+        <v>212541</v>
       </c>
       <c r="AG5" t="n">
-        <v>2359211</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>1065383</v>
+        <v>134142</v>
       </c>
       <c r="AI5" t="n">
-        <v>241827</v>
+        <v>30451</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401615</v>
+        <v>50482</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734838008880615</v>
+        <v>0.9733282327651978</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642236232757568</v>
+        <v>0.9640045166015625</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837440848350525</v>
+        <v>0.9836558699607849</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963029623031616</v>
+        <v>0.9962790012359619</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938694834709167</v>
+        <v>0.993844747543335</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983740448951721</v>
+        <v>0.9983706474304199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>91171</v>
+        <v>16858</v>
       </c>
       <c r="E6" t="n">
-        <v>169016</v>
+        <v>24406</v>
       </c>
       <c r="F6" t="n">
-        <v>153161</v>
+        <v>23691</v>
       </c>
       <c r="G6" t="n">
-        <v>226663</v>
+        <v>13683</v>
       </c>
       <c r="H6" t="n">
-        <v>67858</v>
+        <v>9646</v>
       </c>
       <c r="I6" t="n">
-        <v>6150</v>
+        <v>1320</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>51905</v>
+        <v>6568</v>
       </c>
       <c r="Z6" t="n">
-        <v>42831</v>
+        <v>5365</v>
       </c>
       <c r="AA6" t="n">
-        <v>87352</v>
+        <v>11023</v>
       </c>
       <c r="AB6" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AC6" t="n">
-        <v>55891</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>185</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>10098</v>
+        <v>5204</v>
       </c>
       <c r="E7" t="n">
-        <v>184873</v>
+        <v>57079</v>
       </c>
       <c r="F7" t="n">
-        <v>595057</v>
+        <v>119728</v>
       </c>
       <c r="G7" t="n">
-        <v>295642</v>
+        <v>60971</v>
       </c>
       <c r="H7" t="n">
-        <v>2836252</v>
+        <v>239219</v>
       </c>
       <c r="I7" t="n">
-        <v>155033</v>
+        <v>28668</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>6480</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237812</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60794</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>445</v>
+        <v>58</v>
       </c>
       <c r="D8" t="n">
-        <v>268</v>
+        <v>71</v>
       </c>
       <c r="E8" t="n">
-        <v>13755</v>
+        <v>5332</v>
       </c>
       <c r="F8" t="n">
-        <v>33383</v>
+        <v>10648</v>
       </c>
       <c r="G8" t="n">
-        <v>24976</v>
+        <v>7682</v>
       </c>
       <c r="H8" t="n">
-        <v>386464</v>
+        <v>74419</v>
       </c>
       <c r="I8" t="n">
-        <v>1087831</v>
+        <v>95380</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
